--- a/artfynd/A 45407-2025 artfynd.xlsx
+++ b/artfynd/A 45407-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>131139952</v>
       </c>
       <c r="B3" t="n">
-        <v>57830</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45407-2025 artfynd.xlsx
+++ b/artfynd/A 45407-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>131139952</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45407-2025 artfynd.xlsx
+++ b/artfynd/A 45407-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>131139952</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45407-2025 artfynd.xlsx
+++ b/artfynd/A 45407-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>131139952</v>
       </c>
       <c r="B3" t="n">
-        <v>57834</v>
+        <v>57837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45407-2025 artfynd.xlsx
+++ b/artfynd/A 45407-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>131139952</v>
       </c>
       <c r="B3" t="n">
-        <v>57837</v>
+        <v>57838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45407-2025 artfynd.xlsx
+++ b/artfynd/A 45407-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>131139952</v>
       </c>
       <c r="B3" t="n">
-        <v>57838</v>
+        <v>57844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45407-2025 artfynd.xlsx
+++ b/artfynd/A 45407-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88025529</v>
+        <v>131139952</v>
       </c>
       <c r="B2" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,24 +708,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vidön, Vrm</t>
+          <t>Vidön, Dingelsundet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411436.4112623866</v>
+        <v>411545</v>
       </c>
       <c r="R2" t="n">
-        <v>6578921.578476722</v>
+        <v>6578814</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inte fullvuxen.</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,29 +780,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicole Nelson Nyren</t>
+          <t>Peter Adén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicole Nelson Nyren</t>
+          <t>Peter Adén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131139952</v>
+        <v>113399929</v>
       </c>
       <c r="B3" t="n">
-        <v>57844</v>
+        <v>56689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,16 +809,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>206046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,34 +828,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vidön, Dingelsundet, Vrm</t>
+          <t>Vidön, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411545</v>
+        <v>411740</v>
       </c>
       <c r="R3" t="n">
-        <v>6578814</v>
+        <v>6578144</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,22 +868,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En ko och två kalvar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +903,127 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Adén</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Adén</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>88025529</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vidön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411436</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6578922</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inte fullvuxen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Nicole Nelson Nyren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Nicole Nelson Nyren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
